--- a/templates/05_Labour_Template.xlsx
+++ b/templates/05_Labour_Template.xlsx
@@ -514,7 +514,7 @@
         <v>20.38</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>12</v>
@@ -572,7 +572,7 @@
         <v>17.93</v>
       </c>
       <c r="E3" t="n">
-        <v>417</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>12</v>
@@ -630,7 +630,7 @@
         <v>22.88</v>
       </c>
       <c r="E4" t="n">
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>12</v>
@@ -688,7 +688,7 @@
         <v>19.74</v>
       </c>
       <c r="E5" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>12</v>
@@ -746,7 +746,7 @@
         <v>20.13</v>
       </c>
       <c r="E6" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
@@ -804,7 +804,7 @@
         <v>21.8</v>
       </c>
       <c r="E7" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
@@ -862,7 +862,7 @@
         <v>21.09</v>
       </c>
       <c r="E8" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
@@ -920,7 +920,7 @@
         <v>21.92</v>
       </c>
       <c r="E9" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>12</v>
@@ -978,7 +978,7 @@
         <v>18.2</v>
       </c>
       <c r="E10" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>12</v>
@@ -1036,7 +1036,7 @@
         <v>19.83</v>
       </c>
       <c r="E11" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>12</v>
@@ -1094,7 +1094,7 @@
         <v>22.56</v>
       </c>
       <c r="E12" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>12</v>
@@ -1152,7 +1152,7 @@
         <v>19.82</v>
       </c>
       <c r="E13" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>12</v>
@@ -1210,7 +1210,7 @@
         <v>24.37</v>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>12</v>
@@ -1268,7 +1268,7 @@
         <v>25.14</v>
       </c>
       <c r="E15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>12</v>
@@ -1326,7 +1326,7 @@
         <v>19.32</v>
       </c>
       <c r="E16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>12</v>
@@ -1384,7 +1384,7 @@
         <v>20.8</v>
       </c>
       <c r="E17" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>12</v>
@@ -1442,7 +1442,7 @@
         <v>20.18</v>
       </c>
       <c r="E18" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>12</v>
@@ -1500,7 +1500,7 @@
         <v>23.32</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>12</v>
@@ -1558,7 +1558,7 @@
         <v>24.01</v>
       </c>
       <c r="E20" t="n">
-        <v>646</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>12</v>
@@ -1616,7 +1616,7 @@
         <v>20.49</v>
       </c>
       <c r="E21" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>12</v>
@@ -1674,7 +1674,7 @@
         <v>19.77</v>
       </c>
       <c r="E22" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
         <v>12</v>
@@ -1732,7 +1732,7 @@
         <v>21.91</v>
       </c>
       <c r="E23" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>12</v>
@@ -1790,7 +1790,7 @@
         <v>20.2</v>
       </c>
       <c r="E24" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>12</v>
@@ -1848,7 +1848,7 @@
         <v>22.6</v>
       </c>
       <c r="E25" t="n">
-        <v>346</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
@@ -1906,7 +1906,7 @@
         <v>21.55</v>
       </c>
       <c r="E26" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
         <v>12</v>
@@ -1964,7 +1964,7 @@
         <v>22.17</v>
       </c>
       <c r="E27" t="n">
-        <v>625</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
         <v>12</v>
@@ -2022,7 +2022,7 @@
         <v>19.02</v>
       </c>
       <c r="E28" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
         <v>12</v>
@@ -2080,7 +2080,7 @@
         <v>20.38</v>
       </c>
       <c r="E29" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
         <v>12</v>
@@ -2138,7 +2138,7 @@
         <v>17.99</v>
       </c>
       <c r="E30" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>12</v>
@@ -2196,7 +2196,7 @@
         <v>20.74</v>
       </c>
       <c r="E31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
         <v>12</v>
@@ -2254,7 +2254,7 @@
         <v>17.38</v>
       </c>
       <c r="E32" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>12</v>
@@ -2312,7 +2312,7 @@
         <v>22.4</v>
       </c>
       <c r="E33" t="n">
-        <v>508</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>12</v>
@@ -2370,7 +2370,7 @@
         <v>19.03</v>
       </c>
       <c r="E34" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>12</v>
@@ -2428,7 +2428,7 @@
         <v>23.44</v>
       </c>
       <c r="E35" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>12</v>
@@ -2486,7 +2486,7 @@
         <v>20.68</v>
       </c>
       <c r="E36" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
         <v>12</v>
@@ -2544,7 +2544,7 @@
         <v>17.64</v>
       </c>
       <c r="E37" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F37" t="n">
         <v>12</v>
@@ -2602,7 +2602,7 @@
         <v>20.67</v>
       </c>
       <c r="E38" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
         <v>12</v>
@@ -2660,7 +2660,7 @@
         <v>18.58</v>
       </c>
       <c r="E39" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>12</v>
@@ -2718,7 +2718,7 @@
         <v>18.62</v>
       </c>
       <c r="E40" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>12</v>
@@ -2776,7 +2776,7 @@
         <v>21.58</v>
       </c>
       <c r="E41" t="n">
-        <v>550</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>12</v>
@@ -2834,7 +2834,7 @@
         <v>19.97</v>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>12</v>
@@ -2892,7 +2892,7 @@
         <v>21.32</v>
       </c>
       <c r="E43" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
         <v>12</v>
@@ -2950,7 +2950,7 @@
         <v>19.41</v>
       </c>
       <c r="E44" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
         <v>12</v>
@@ -3008,7 +3008,7 @@
         <v>19.85</v>
       </c>
       <c r="E45" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>12</v>
@@ -3066,7 +3066,7 @@
         <v>19.63</v>
       </c>
       <c r="E46" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>12</v>
@@ -3124,7 +3124,7 @@
         <v>21.97</v>
       </c>
       <c r="E47" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
         <v>12</v>
@@ -3182,7 +3182,7 @@
         <v>18.93</v>
       </c>
       <c r="E48" t="n">
-        <v>125</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
         <v>12</v>
@@ -3240,7 +3240,7 @@
         <v>21.33</v>
       </c>
       <c r="E49" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
         <v>12</v>
@@ -3298,7 +3298,7 @@
         <v>21.64</v>
       </c>
       <c r="E50" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
         <v>12</v>
@@ -3356,7 +3356,7 @@
         <v>22.46</v>
       </c>
       <c r="E51" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F51" t="n">
         <v>12</v>
@@ -3414,7 +3414,7 @@
         <v>21.16</v>
       </c>
       <c r="E52" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
         <v>12</v>
@@ -3472,7 +3472,7 @@
         <v>20.27</v>
       </c>
       <c r="E53" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>12</v>
@@ -3530,7 +3530,7 @@
         <v>20.1</v>
       </c>
       <c r="E54" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
         <v>12</v>
@@ -3588,7 +3588,7 @@
         <v>18.58</v>
       </c>
       <c r="E55" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
         <v>12</v>
@@ -3646,7 +3646,7 @@
         <v>18.73</v>
       </c>
       <c r="E56" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>12</v>
@@ -3704,7 +3704,7 @@
         <v>20.6</v>
       </c>
       <c r="E57" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
         <v>12</v>
@@ -3762,7 +3762,7 @@
         <v>22.7</v>
       </c>
       <c r="E58" t="n">
-        <v>658</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
         <v>12</v>
@@ -3820,7 +3820,7 @@
         <v>20.12</v>
       </c>
       <c r="E59" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
         <v>12</v>
@@ -3878,7 +3878,7 @@
         <v>23.75</v>
       </c>
       <c r="E60" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
         <v>12</v>
@@ -3936,7 +3936,7 @@
         <v>19.19</v>
       </c>
       <c r="E61" t="n">
-        <v>6500</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
         <v>12</v>
@@ -3994,7 +3994,7 @@
         <v>20.74</v>
       </c>
       <c r="E62" t="n">
-        <v>258</v>
+        <v>0</v>
       </c>
       <c r="F62" t="n">
         <v>12</v>
@@ -4052,7 +4052,7 @@
         <v>18.26</v>
       </c>
       <c r="E63" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>12</v>
@@ -4110,7 +4110,7 @@
         <v>22.96</v>
       </c>
       <c r="E64" t="n">
-        <v>708</v>
+        <v>0</v>
       </c>
       <c r="F64" t="n">
         <v>12</v>
@@ -4168,7 +4168,7 @@
         <v>22.23</v>
       </c>
       <c r="E65" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="F65" t="n">
         <v>12</v>
@@ -4226,7 +4226,7 @@
         <v>23.65</v>
       </c>
       <c r="E66" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>12</v>
@@ -4284,7 +4284,7 @@
         <v>21.56</v>
       </c>
       <c r="E67" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F67" t="n">
         <v>12</v>
@@ -4342,7 +4342,7 @@
         <v>20.99</v>
       </c>
       <c r="E68" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F68" t="n">
         <v>12</v>
@@ -4400,7 +4400,7 @@
         <v>21.94</v>
       </c>
       <c r="E69" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="F69" t="n">
         <v>12</v>
